--- a/data/tags/אלבומים חדשים/sites/rotter/2026-02-week04/titles.xlsx
+++ b/data/tags/אלבומים חדשים/sites/rotter/2026-02-week04/titles.xlsx
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>רותם כהן - הבן של נורית</v>
+        <v>רינת בר - 300 EP</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-02-20</v>
+        <v>2026-02-24</v>
       </c>
       <c r="C2" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24452&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24455&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-02-23</v>
+        <v>2026-02-24</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>13:35</v>
+        <v>22:41</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>רותם כהן - הבן של נורית</v>
+        <v>רינת בר - 300 EP</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/אלבומים חדשים/sites/rotter/2026-02-week04/titles.xlsx
+++ b/data/tags/אלבומים חדשים/sites/rotter/2026-02-week04/titles.xlsx
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>רינת בר - 300 EP</v>
+        <v>אפרת גוש - לרדוף אחרי השמש</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-02-24</v>
+        <v>2026-02-25</v>
       </c>
       <c r="C2" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24455&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24456&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-02-24</v>
+        <v>2026-02-25</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>22:41</v>
+        <v>15:20</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>רינת בר - 300 EP</v>
+        <v>אפרת גוש - לרדוף אחרי השמש</v>
       </c>
     </row>
   </sheetData>
